--- a/MateriaisBasicos.xlsx
+++ b/MateriaisBasicos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Matheus\Desktop\Indicadores\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://osborne1-my.sharepoint.com/personal/matheus_almeida_osborne_com_br/Documents/Área de Trabalho/Indicadores/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C3E65EB-8FDC-44CF-A879-823FBE1A2E77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{3C3E65EB-8FDC-44CF-A879-823FBE1A2E77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{52C41F19-691D-459F-B8AE-932BE23A2ADD}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="689" xr2:uid="{023A7886-F42D-4B94-A790-9D3B132CC588}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="262">
   <si>
     <t>J.05.0001</t>
   </si>
@@ -798,6 +798,33 @@
   </si>
   <si>
     <t>PU 40  FLEX ADESIVO DE POLIURETANO DE CURA RÁPIDA COR BRANCO  TUBO 310ML</t>
+  </si>
+  <si>
+    <t>EPI</t>
+  </si>
+  <si>
+    <t>Ferramenta</t>
+  </si>
+  <si>
+    <t>Material agregado</t>
+  </si>
+  <si>
+    <t>Material Agregado</t>
+  </si>
+  <si>
+    <t>Material de limpeza</t>
+  </si>
+  <si>
+    <t>Material diversos</t>
+  </si>
+  <si>
+    <t>Material elétrico</t>
+  </si>
+  <si>
+    <t>Material proteção</t>
+  </si>
+  <si>
+    <t>Classificação</t>
   </si>
 </sst>
 </file>
@@ -1211,17 +1238,17 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C139"/>
+  <dimension ref="A1:D139"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.77734375" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="91" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>207</v>
       </c>
@@ -1231,8 +1258,11 @@
       <c r="C1" s="6" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D1" s="6" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -1242,8 +1272,11 @@
       <c r="C2" s="2" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D2" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <f t="shared" ref="A3:A17" si="0">A2+1</f>
         <v>2</v>
@@ -1254,8 +1287,11 @@
       <c r="C3" s="2" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D3" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -1266,8 +1302,11 @@
       <c r="C4" s="2" t="s">
         <v>234</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D4" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -1278,8 +1317,11 @@
       <c r="C5" s="2" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D5" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -1290,8 +1332,11 @@
       <c r="C6" s="2" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D6" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -1302,8 +1347,11 @@
       <c r="C7" s="2" t="s">
         <v>222</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D7" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -1314,8 +1362,11 @@
       <c r="C8" s="2" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D8" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -1326,8 +1377,11 @@
       <c r="C9" s="2" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D9" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -1338,8 +1392,11 @@
       <c r="C10" s="2" t="s">
         <v>226</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D10" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -1350,8 +1407,11 @@
       <c r="C11" s="2" t="s">
         <v>228</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D11" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -1362,8 +1422,11 @@
       <c r="C12" s="2" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D12" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -1374,8 +1437,11 @@
       <c r="C13" s="2" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D13" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -1386,8 +1452,11 @@
       <c r="C14" s="2" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D14" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -1398,8 +1467,11 @@
       <c r="C15" s="2" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D15" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -1410,8 +1482,11 @@
       <c r="C16" s="2" t="s">
         <v>221</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D16" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -1422,8 +1497,11 @@
       <c r="C17" s="2" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D17" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
         <f t="shared" ref="A18:A49" si="1">A17+1</f>
         <v>17</v>
@@ -1434,8 +1512,11 @@
       <c r="C18" s="2" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D18" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <f t="shared" si="1"/>
         <v>18</v>
@@ -1446,8 +1527,11 @@
       <c r="C19" s="2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D19" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
         <f t="shared" si="1"/>
         <v>19</v>
@@ -1458,8 +1542,11 @@
       <c r="C20" s="2" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D20" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
         <f t="shared" si="1"/>
         <v>20</v>
@@ -1470,8 +1557,11 @@
       <c r="C21" s="2" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D21" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
         <f t="shared" si="1"/>
         <v>21</v>
@@ -1482,8 +1572,11 @@
       <c r="C22" s="2" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D22" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
         <f t="shared" si="1"/>
         <v>22</v>
@@ -1494,8 +1587,11 @@
       <c r="C23" s="2" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D23" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
         <f t="shared" si="1"/>
         <v>23</v>
@@ -1506,8 +1602,11 @@
       <c r="C24" s="2" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D24" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
         <f t="shared" si="1"/>
         <v>24</v>
@@ -1518,8 +1617,11 @@
       <c r="C25" s="2" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D25" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
         <f t="shared" si="1"/>
         <v>25</v>
@@ -1530,8 +1632,11 @@
       <c r="C26" s="2" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D26" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
         <f t="shared" si="1"/>
         <v>26</v>
@@ -1542,8 +1647,11 @@
       <c r="C27" s="2" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D27" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="3">
         <f t="shared" si="1"/>
         <v>27</v>
@@ -1554,8 +1662,11 @@
       <c r="C28" s="2" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D28" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="3">
         <f t="shared" si="1"/>
         <v>28</v>
@@ -1566,8 +1677,11 @@
       <c r="C29" s="2" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D29" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="3">
         <f t="shared" si="1"/>
         <v>29</v>
@@ -1578,8 +1692,11 @@
       <c r="C30" s="2" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D30" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
         <f t="shared" si="1"/>
         <v>30</v>
@@ -1590,8 +1707,11 @@
       <c r="C31" s="2" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D31" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="3">
         <f t="shared" si="1"/>
         <v>31</v>
@@ -1602,8 +1722,11 @@
       <c r="C32" s="2" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D32" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="3">
         <f t="shared" si="1"/>
         <v>32</v>
@@ -1614,8 +1737,11 @@
       <c r="C33" s="2" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D33" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="3">
         <f t="shared" si="1"/>
         <v>33</v>
@@ -1626,8 +1752,11 @@
       <c r="C34" s="2" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D34" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="3">
         <f t="shared" si="1"/>
         <v>34</v>
@@ -1638,8 +1767,11 @@
       <c r="C35" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D35" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="3">
         <f t="shared" si="1"/>
         <v>35</v>
@@ -1650,8 +1782,11 @@
       <c r="C36" s="2" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D36" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="3">
         <f t="shared" si="1"/>
         <v>36</v>
@@ -1662,8 +1797,11 @@
       <c r="C37" s="2" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D37" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="3">
         <f t="shared" si="1"/>
         <v>37</v>
@@ -1674,8 +1812,11 @@
       <c r="C38" s="2" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D38" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="3">
         <f t="shared" si="1"/>
         <v>38</v>
@@ -1686,8 +1827,11 @@
       <c r="C39" s="2" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D39" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="3">
         <f t="shared" si="1"/>
         <v>39</v>
@@ -1698,8 +1842,11 @@
       <c r="C40" s="2" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D40" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="3">
         <f t="shared" si="1"/>
         <v>40</v>
@@ -1710,8 +1857,11 @@
       <c r="C41" s="2" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D41" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="3">
         <f t="shared" si="1"/>
         <v>41</v>
@@ -1722,8 +1872,11 @@
       <c r="C42" s="2" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D42" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="3">
         <f t="shared" si="1"/>
         <v>42</v>
@@ -1734,8 +1887,11 @@
       <c r="C43" s="2" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D43" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="3">
         <f t="shared" si="1"/>
         <v>43</v>
@@ -1746,8 +1902,11 @@
       <c r="C44" s="2" t="s">
         <v>235</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D44" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="3">
         <f t="shared" si="1"/>
         <v>44</v>
@@ -1758,8 +1917,11 @@
       <c r="C45" s="2" t="s">
         <v>244</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D45" s="2" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="3">
         <f t="shared" si="1"/>
         <v>45</v>
@@ -1770,8 +1932,11 @@
       <c r="C46" s="2" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D46" s="2" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="3">
         <f t="shared" si="1"/>
         <v>46</v>
@@ -1782,8 +1947,11 @@
       <c r="C47" s="2" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D47" s="2" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="3">
         <f t="shared" si="1"/>
         <v>47</v>
@@ -1794,8 +1962,11 @@
       <c r="C48" s="2" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D48" s="2" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="3">
         <f t="shared" si="1"/>
         <v>48</v>
@@ -1806,8 +1977,11 @@
       <c r="C49" s="2" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D49" s="2" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="3">
         <f t="shared" ref="A50:A81" si="2">A49+1</f>
         <v>49</v>
@@ -1818,8 +1992,11 @@
       <c r="C50" s="2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D50" s="2" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="3">
         <f t="shared" si="2"/>
         <v>50</v>
@@ -1830,8 +2007,11 @@
       <c r="C51" s="2" t="s">
         <v>229</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D51" s="2" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="3">
         <f t="shared" si="2"/>
         <v>51</v>
@@ -1842,8 +2022,11 @@
       <c r="C52" s="2" t="s">
         <v>242</v>
       </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D52" s="2" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="3">
         <f t="shared" si="2"/>
         <v>52</v>
@@ -1854,8 +2037,11 @@
       <c r="C53" s="2" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D53" s="2" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="3">
         <f t="shared" si="2"/>
         <v>53</v>
@@ -1866,8 +2052,11 @@
       <c r="C54" s="2" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D54" s="2" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="3">
         <f t="shared" si="2"/>
         <v>54</v>
@@ -1878,8 +2067,11 @@
       <c r="C55" s="2" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D55" s="2" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="3">
         <f t="shared" si="2"/>
         <v>55</v>
@@ -1890,8 +2082,11 @@
       <c r="C56" s="2" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D56" s="2" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="3">
         <f t="shared" si="2"/>
         <v>56</v>
@@ -1902,8 +2097,11 @@
       <c r="C57" s="2" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D57" s="2" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="3">
         <f t="shared" si="2"/>
         <v>57</v>
@@ -1914,8 +2112,11 @@
       <c r="C58" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D58" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="3">
         <f t="shared" si="2"/>
         <v>58</v>
@@ -1926,8 +2127,11 @@
       <c r="C59" s="2" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D59" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" s="3">
         <f t="shared" si="2"/>
         <v>59</v>
@@ -1938,8 +2142,11 @@
       <c r="C60" s="2" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D60" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" s="3">
         <f t="shared" si="2"/>
         <v>60</v>
@@ -1950,8 +2157,11 @@
       <c r="C61" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D61" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" s="3">
         <f t="shared" si="2"/>
         <v>61</v>
@@ -1962,8 +2172,11 @@
       <c r="C62" s="2" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D62" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" s="3">
         <f t="shared" si="2"/>
         <v>62</v>
@@ -1974,8 +2187,11 @@
       <c r="C63" s="2" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D63" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="3">
         <f t="shared" si="2"/>
         <v>63</v>
@@ -1986,8 +2202,11 @@
       <c r="C64" s="2" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D64" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" s="3">
         <f t="shared" si="2"/>
         <v>64</v>
@@ -1998,8 +2217,11 @@
       <c r="C65" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D65" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" s="3">
         <f t="shared" si="2"/>
         <v>65</v>
@@ -2010,8 +2232,11 @@
       <c r="C66" s="2" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D66" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" s="3">
         <f t="shared" si="2"/>
         <v>66</v>
@@ -2022,8 +2247,11 @@
       <c r="C67" s="2" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D67" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" s="3">
         <f t="shared" si="2"/>
         <v>67</v>
@@ -2034,8 +2262,11 @@
       <c r="C68" s="2" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D68" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" s="3">
         <f t="shared" si="2"/>
         <v>68</v>
@@ -2046,8 +2277,11 @@
       <c r="C69" s="2" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D69" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" s="3">
         <f t="shared" si="2"/>
         <v>69</v>
@@ -2058,8 +2292,11 @@
       <c r="C70" s="2" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D70" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" s="3">
         <f t="shared" si="2"/>
         <v>70</v>
@@ -2070,8 +2307,11 @@
       <c r="C71" s="2" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D71" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" s="3">
         <f t="shared" si="2"/>
         <v>71</v>
@@ -2082,8 +2322,11 @@
       <c r="C72" s="1" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D72" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" s="3">
         <f t="shared" si="2"/>
         <v>72</v>
@@ -2094,8 +2337,11 @@
       <c r="C73" s="2" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D73" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" s="3">
         <f t="shared" si="2"/>
         <v>73</v>
@@ -2106,8 +2352,11 @@
       <c r="C74" s="2" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D74" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" s="3">
         <f t="shared" si="2"/>
         <v>74</v>
@@ -2118,8 +2367,11 @@
       <c r="C75" s="2" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D75" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" s="3">
         <f t="shared" si="2"/>
         <v>75</v>
@@ -2130,8 +2382,11 @@
       <c r="C76" s="2" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D76" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" s="3">
         <f t="shared" si="2"/>
         <v>76</v>
@@ -2142,8 +2397,11 @@
       <c r="C77" s="2" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D77" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" s="3">
         <f t="shared" si="2"/>
         <v>77</v>
@@ -2154,8 +2412,11 @@
       <c r="C78" s="2" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D78" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" s="3">
         <f t="shared" si="2"/>
         <v>78</v>
@@ -2166,8 +2427,11 @@
       <c r="C79" s="2" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D79" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" s="3">
         <f t="shared" si="2"/>
         <v>79</v>
@@ -2178,8 +2442,11 @@
       <c r="C80" s="2" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D80" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" s="3">
         <f t="shared" si="2"/>
         <v>80</v>
@@ -2190,8 +2457,11 @@
       <c r="C81" s="2" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D81" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" s="3">
         <f t="shared" ref="A82:A114" si="3">A81+1</f>
         <v>81</v>
@@ -2202,8 +2472,11 @@
       <c r="C82" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D82" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" s="3">
         <f t="shared" si="3"/>
         <v>82</v>
@@ -2214,8 +2487,11 @@
       <c r="C83" s="2" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D83" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" s="3">
         <f t="shared" si="3"/>
         <v>83</v>
@@ -2226,8 +2502,11 @@
       <c r="C84" s="2" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D84" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" s="3">
         <f t="shared" si="3"/>
         <v>84</v>
@@ -2238,8 +2517,11 @@
       <c r="C85" s="2" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D85" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" s="3">
         <f t="shared" si="3"/>
         <v>85</v>
@@ -2250,8 +2532,11 @@
       <c r="C86" s="2" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D86" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" s="3">
         <f t="shared" si="3"/>
         <v>86</v>
@@ -2262,8 +2547,11 @@
       <c r="C87" s="2" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D87" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" s="3">
         <f t="shared" si="3"/>
         <v>87</v>
@@ -2274,8 +2562,11 @@
       <c r="C88" s="2" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D88" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89" s="3">
         <f t="shared" si="3"/>
         <v>88</v>
@@ -2286,8 +2577,11 @@
       <c r="C89" s="2" t="s">
         <v>241</v>
       </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D89" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90" s="3">
         <f t="shared" si="3"/>
         <v>89</v>
@@ -2298,8 +2592,11 @@
       <c r="C90" s="2" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D90" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91" s="3">
         <f t="shared" si="3"/>
         <v>90</v>
@@ -2310,8 +2607,11 @@
       <c r="C91" s="2" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D91" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92" s="3">
         <f t="shared" si="3"/>
         <v>91</v>
@@ -2322,8 +2622,11 @@
       <c r="C92" s="2" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D92" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" s="3">
         <f t="shared" si="3"/>
         <v>92</v>
@@ -2334,8 +2637,11 @@
       <c r="C93" s="2" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D93" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94" s="3">
         <f t="shared" si="3"/>
         <v>93</v>
@@ -2346,8 +2652,11 @@
       <c r="C94" s="2" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D94" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95" s="3">
         <f t="shared" si="3"/>
         <v>94</v>
@@ -2358,8 +2667,11 @@
       <c r="C95" s="2" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D95" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96" s="3">
         <f t="shared" si="3"/>
         <v>95</v>
@@ -2370,8 +2682,11 @@
       <c r="C96" s="2" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D96" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97" s="3">
         <f t="shared" si="3"/>
         <v>96</v>
@@ -2382,8 +2697,11 @@
       <c r="C97" s="2" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D97" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98" s="3">
         <f t="shared" si="3"/>
         <v>97</v>
@@ -2394,8 +2712,11 @@
       <c r="C98" s="2" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D98" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99" s="3">
         <f t="shared" si="3"/>
         <v>98</v>
@@ -2406,8 +2727,11 @@
       <c r="C99" s="2" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D99" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100" s="3">
         <f t="shared" si="3"/>
         <v>99</v>
@@ -2418,8 +2742,11 @@
       <c r="C100" s="2" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D100" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101" s="3">
         <f t="shared" si="3"/>
         <v>100</v>
@@ -2430,8 +2757,11 @@
       <c r="C101" s="2" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D101" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102" s="3">
         <f t="shared" si="3"/>
         <v>101</v>
@@ -2442,8 +2772,11 @@
       <c r="C102" s="2" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D102" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A103" s="3">
         <f t="shared" si="3"/>
         <v>102</v>
@@ -2454,8 +2787,11 @@
       <c r="C103" s="2" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D103" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A104" s="3">
         <f t="shared" si="3"/>
         <v>103</v>
@@ -2466,8 +2802,11 @@
       <c r="C104" s="2" t="s">
         <v>252</v>
       </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D104" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A105" s="3">
         <f t="shared" si="3"/>
         <v>104</v>
@@ -2478,8 +2817,11 @@
       <c r="C105" s="2" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D105" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A106" s="3">
         <f t="shared" si="3"/>
         <v>105</v>
@@ -2490,8 +2832,11 @@
       <c r="C106" s="2" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D106" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107" s="3">
         <f t="shared" si="3"/>
         <v>106</v>
@@ -2502,8 +2847,11 @@
       <c r="C107" s="2" t="s">
         <v>251</v>
       </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D107" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A108" s="3">
         <f t="shared" si="3"/>
         <v>107</v>
@@ -2514,8 +2862,11 @@
       <c r="C108" s="2" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D108" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A109" s="3">
         <f t="shared" si="3"/>
         <v>108</v>
@@ -2526,8 +2877,11 @@
       <c r="C109" s="2" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D109" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A110" s="3">
         <f t="shared" si="3"/>
         <v>109</v>
@@ -2538,8 +2892,11 @@
       <c r="C110" s="2" t="s">
         <v>250</v>
       </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D110" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A111" s="3">
         <f t="shared" si="3"/>
         <v>110</v>
@@ -2550,8 +2907,11 @@
       <c r="C111" s="2" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D111" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A112" s="3">
         <f t="shared" si="3"/>
         <v>111</v>
@@ -2562,8 +2922,11 @@
       <c r="C112" s="2" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D112" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A113" s="3">
         <f t="shared" si="3"/>
         <v>112</v>
@@ -2574,8 +2937,11 @@
       <c r="C113" s="2" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D113" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A114" s="3">
         <f t="shared" si="3"/>
         <v>113</v>
@@ -2586,8 +2952,11 @@
       <c r="C114" s="2" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D114" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A115" s="3">
         <f t="shared" ref="A115:A126" si="4">A114+1</f>
         <v>114</v>
@@ -2598,8 +2967,11 @@
       <c r="C115" s="2" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D115" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A116" s="3">
         <f t="shared" si="4"/>
         <v>115</v>
@@ -2610,8 +2982,11 @@
       <c r="C116" s="2" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D116" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A117" s="3">
         <f t="shared" si="4"/>
         <v>116</v>
@@ -2622,8 +2997,11 @@
       <c r="C117" s="2" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D117" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A118" s="3">
         <f t="shared" si="4"/>
         <v>117</v>
@@ -2634,8 +3012,11 @@
       <c r="C118" s="2" t="s">
         <v>246</v>
       </c>
-    </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D118" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A119" s="3">
         <f t="shared" si="4"/>
         <v>118</v>
@@ -2646,8 +3027,11 @@
       <c r="C119" s="2" t="s">
         <v>247</v>
       </c>
-    </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D119" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A120" s="3">
         <f t="shared" si="4"/>
         <v>119</v>
@@ -2658,8 +3042,11 @@
       <c r="C120" s="2" t="s">
         <v>248</v>
       </c>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D120" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A121" s="3">
         <f t="shared" si="4"/>
         <v>120</v>
@@ -2670,8 +3057,11 @@
       <c r="C121" s="2" t="s">
         <v>249</v>
       </c>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D121" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A122" s="3">
         <f t="shared" si="4"/>
         <v>121</v>
@@ -2682,8 +3072,11 @@
       <c r="C122" s="2" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D122" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A123" s="3">
         <f t="shared" si="4"/>
         <v>122</v>
@@ -2694,8 +3087,11 @@
       <c r="C123" s="2" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D123" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A124" s="3">
         <f t="shared" si="4"/>
         <v>123</v>
@@ -2706,8 +3102,11 @@
       <c r="C124" s="2" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D124" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A125" s="3">
         <f t="shared" si="4"/>
         <v>124</v>
@@ -2718,8 +3117,11 @@
       <c r="C125" s="2" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D125" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A126" s="3">
         <f t="shared" si="4"/>
         <v>125</v>
@@ -2729,6 +3131,9 @@
       </c>
       <c r="C126" s="2" t="s">
         <v>5</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.3">
